--- a/data/trans_bre/IP43-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP43-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 7,94</t>
+          <t>-10,0; 8,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 7,66</t>
+          <t>-7,29; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -649,12 +649,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 30,77</t>
+          <t>-28,81; 33,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 61,41</t>
+          <t>-36,88; 60,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 6,13</t>
+          <t>-9,04; 5,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 5,61</t>
+          <t>-6,19; 5,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 21,68</t>
+          <t>-24,32; 17,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,38; 38,35</t>
+          <t>-30,23; 34,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 6,44</t>
+          <t>-6,26; 7,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 5,18</t>
+          <t>-3,12; 5,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 48,47</t>
+          <t>-33,45; 56,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,8; 158,31</t>
+          <t>-43,68; 142,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 7,7</t>
+          <t>-3,62; 7,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 7,79</t>
+          <t>-1,28; 7,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 83,08</t>
+          <t>-24,33; 73,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 171,05</t>
+          <t>-18,44; 150,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,81</t>
+          <t>-4,12; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,6</t>
+          <t>-1,72; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 13,21</t>
+          <t>-16,38; 13,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 35,85</t>
+          <t>-13,83; 35,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
